--- a/daily_matches/job_matches_2026-07-23.xlsx
+++ b/daily_matches/job_matches_2026-07-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ontario, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, Glue, Athena, Redshift, Data Lake, Kinesis, CI/CD</t>
+          <t>RAG, Glue, Athena, BigQuery, Data Lake, Dataflow, Jenkins, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b55a448295d9621</t>
+          <t>https://www.indeed.com/viewjob?jk=671918da9a59fae2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MTS 1, Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, PostgreSQL, MySQL</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Kinesis, FastAPI, Kubernetes, CI/CD, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e64db4399512f1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a032c85f3eda4c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, Glue, Athena, Redshift, Data Lake, Kinesis, CI/CD</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Kinesis, FastAPI, Kubernetes, CI/CD, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63c45c243678d800</t>
+          <t>https://www.indeed.com/viewjob?jk=3c86483f8d64a717</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vision Radiology</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Data Lake, Git, Snowflake, BigQuery, Redshift, Kafka, Tableau</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Kinesis, FastAPI, Kubernetes, CI/CD, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea77e5dc301d8192</t>
+          <t>https://www.indeed.com/viewjob?jk=e99d5df04ef88554</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Productization Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, MLflow, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform, Git, Databricks</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Kinesis, FastAPI, Kubernetes, CI/CD, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85be9fd2c83ec659</t>
+          <t>https://www.indeed.com/viewjob?jk=3b9ee82ed408549d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Research Full Stack Coder</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Brown University Health</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, TensorFlow, PyTorch, Docker, Kubernetes, Git, NoSQL, Python, SQL</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Kinesis, FastAPI, Kubernetes, CI/CD, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c62e268910551ce</t>
+          <t>https://www.indeed.com/viewjob?jk=1509df6902e78ef9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sales Engineer – AI &amp; Agentic Sales Systems</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WRS Health</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Prompt Engineering, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Kinesis, FastAPI, Kubernetes, CI/CD, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8cc43499d786a9</t>
+          <t>https://www.indeed.com/viewjob?jk=06c709837f56a222</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, MongoDB, SQL, R, Java</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Kinesis, FastAPI, Kubernetes, CI/CD, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec5539efbd14b991</t>
+          <t>https://www.indeed.com/viewjob?jk=af8d2486638678d0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, Jenkins, Git, Kafka, NoSQL, SQL, R</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Kinesis, FastAPI, Kubernetes, CI/CD, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff6fde999db22d09</t>
+          <t>https://www.indeed.com/viewjob?jk=7cb53465712420c3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI / Polyglot Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mitsui Sumitomo Insurance Group</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Kafka, Python</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Kinesis, FastAPI, Kubernetes, CI/CD, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d375c5ea5a7a76</t>
+          <t>https://www.indeed.com/viewjob?jk=31c8974b5b1919e3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fischer Homes</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Erlanger, KY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, Synapse, CI/CD, Git, Snowflake, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Kinesis, FastAPI, Kubernetes, CI/CD, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2efeb3f6963e2ac9</t>
+          <t>https://www.indeed.com/viewjob?jk=4ad48f14142dbd8d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer- Backend</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Kafka, Cassandra, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Kinesis, FastAPI, Kubernetes, CI/CD, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35a9bdaf3bc67a1</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee559eb028fc26b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist II, Anti Money Laundering Transaction Monitoring</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Git, Databricks, Hadoop, Python, SQL, R</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Kinesis, FastAPI, Kubernetes, CI/CD, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a476ab4de66d582</t>
+          <t>https://www.indeed.com/viewjob?jk=cae138f9046f28a0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer 2</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, PyTorch, Git, Hadoop, Python, SQL, R, Scala, A/B Testing</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, Kinesis, FastAPI, Kubernetes, CI/CD, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7f10b26a417d2c3</t>
+          <t>https://www.indeed.com/viewjob?jk=ea174bb985cdf126</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CI/CD, Git, MySQL, MongoDB, NoSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, S3, EC2, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7d3a54b05fedd23</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc5301813e35e61</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Engineer / LLM Developer (Microsoft Foundry)</t>
+          <t>Senior Site Reliability Engineer ( SRE)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Power BI, Python, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1b38a52798fcff4</t>
+          <t>https://www.indeed.com/viewjob?jk=1c1097e65f054454</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, PostgreSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Data Lake, CI/CD, Jenkins, Terraform, Git, Snowflake, Databricks, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c88e964fc6c7f01</t>
+          <t>https://www.indeed.com/viewjob?jk=3e670639c0e140f2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Data Governance &amp; AI Enablement</t>
+          <t>Compliance Engineering, Software Engineer, Associate, Dallas</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Snowflake, Databricks, Tableau, Power BI, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Prompt Engineering, Data Lake, Kubernetes, Git, Snowflake, PySpark, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c7649f5d49c6be2</t>
+          <t>https://www.indeed.com/viewjob?jk=168ff3065ccc219c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Technical Services Engineer</t>
+          <t>Software Engineering - Data, Lakehouse and AI Data Platform Engineer - Associate - New York</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, MongoDB, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Snowflake, Databricks, Kafka, Hadoop, Python, SQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115f6aff7f0821f6</t>
+          <t>https://www.indeed.com/viewjob?jk=74433be930df41f9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EverHealth - Software Engineer (Remote, US)</t>
+          <t>Senior Engineer, Applied AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, Git, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964a319d38182888</t>
+          <t>https://www.indeed.com/viewjob?jk=37d306f6e35b6d71</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer, Infrastructure Programs</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>LEMNIS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, CI/CD, Kafka, PostgreSQL, SQL, R, Scala, Optimization</t>
+          <t>RAG, Cortex, Redshift, BigQuery, CI/CD, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d6083c70976741</t>
+          <t>https://www.indeed.com/viewjob?jk=7fde3a175948d71c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineering - Data, Lakehouse and AI Data Platform Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Snowflake, Databricks, Kafka, Hadoop, Python, SQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1766c4af77fd1114</t>
+          <t>https://www.indeed.com/viewjob?jk=f4361b7290689784</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CurbWaste</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Java</t>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03ed3fd0cc93d245</t>
+          <t>https://www.indeed.com/viewjob?jk=2a38962865d9b9fe</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer - Vehicle Configuration Optimization</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Beacon Biosignals</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, Data Lake, Snowflake, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Kinesis, Kubernetes, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac80ea93a8c7bea4</t>
+          <t>https://www.indeed.com/viewjob?jk=23309b822ab0340b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BI Reporting Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Data Society</t>
+          <t>Beacon Biosignals</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Copilot, Synapse, CI/CD, Git, Databricks, Tableau, Power BI, SQL, R</t>
+          <t>RAG, Kinesis, Kubernetes, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d7772ddc47558e</t>
+          <t>https://www.indeed.com/viewjob?jk=791ec2106c13eccd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MTS 1, Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Beacon Biosignals</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CI/CD, Jenkins, Git, Kafka, MongoDB, SQL, R, Java, Scala</t>
+          <t>RAG, Kinesis, Kubernetes, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bad747180322f315</t>
+          <t>https://www.indeed.com/viewjob?jk=d4a8ff54da8fab62</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Beacon Biosignals</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, Python, R, Java</t>
+          <t>RAG, Kinesis, Kubernetes, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea97fd5ad244ab0</t>
+          <t>https://www.indeed.com/viewjob?jk=027563babe2da263</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Beacon Biosignals</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
+          <t>RAG, Kinesis, Kubernetes, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1635164fe0c734d7</t>
+          <t>https://www.indeed.com/viewjob?jk=387872be90aa75e5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Beacon Biosignals</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Git, Hadoop, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Kinesis, Kubernetes, Terraform, Git, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4537e91e2c05d24</t>
+          <t>https://www.indeed.com/viewjob?jk=413b65437c04a0c6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Agentic AI Software Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bread Financial</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, Copilot, Git, Python, R, Scala</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec080ce46843f2cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2a30034eedf02862</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Manufacturing Data Scientist</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Allfast Fastening Systems</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Julia, Optimization</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,172 +1546,172 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=045b3c0021f36f48</t>
+          <t>https://www.indeed.com/viewjob?jk=5eccfdb444cc8e27</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer II Platform, Core Services</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, CI/CD, Git, Snowflake, SQL, R, Scala</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, Kafka, R</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa4a363126d55a5</t>
+          <t>https://www.indeed.com/viewjob?jk=80eeb9192292b91b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Premera Blue Cross</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, CI/CD, Git, Snowflake, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Matplotlib, Python, R</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d15deb3e404a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=ad885ef290cec9b6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Computational Biology MLOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, CI/CD, Git, Snowflake, SQL, R, Scala</t>
+          <t>LangChain, TensorFlow, PyTorch, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee11137ef52cb109</t>
+          <t>https://www.indeed.com/viewjob?jk=d947b628f5086b9a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Computational Biology MLOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Databricks, PySpark, Python, SQL, R, Optimization</t>
+          <t>LangChain, TensorFlow, PyTorch, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fcc0d34e0347fd</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ee4ceb255cfe54</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Analytics and Research Analyst</t>
+          <t>Senior EDI Application Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, S3, Jenkins, Git, MySQL, MongoDB, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f6680771dce9ba3</t>
+          <t>https://www.indeed.com/viewjob?jk=465fd14b442dff3e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Analytics and Research Analyst</t>
+          <t>Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,42 +1756,952 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1b3a4ffc5fc5c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ac325e7e9d3a0d47</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Developer: Back End Focus</t>
+          <t>Java Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EGW Personnel</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4223ba3d2859bb79</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Master Data Architect</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Baker Hughes</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, S3, Data Lake, Git, Databricks, Kafka, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e705242041dfe23d</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Local Search &amp; Marketplace</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Newsbreak</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, Kubernetes, Python, R, Java, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2119bac79dda29dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Local Search &amp; Marketplace</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Newsbreak</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, Kubernetes, Python, R, Java, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4879cda319bf2ecd</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Instabase</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Docker, Kubernetes, Kafka, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21064dcf824fc8d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Data Engineer, Senior</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Blue Shield of California</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, CI/CD, Git, Snowflake, Databricks, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69813b52ae6b9ff3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Databricks Database Administrator</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Curana Health</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f43201437dfa1144</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Coralogix</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
         <v>10</v>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0005b18918c48350</t>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Kafka, PostgreSQL, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22020277d4fddb31</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Systems Engineer, Data Center AI</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=297fae0710cb42ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AI Engineer IV</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Premera Blue Cross</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Matplotlib, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93fe9c85608a1e71</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Palantir AI engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Prodapt Solutions</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d97e7060c05c7978</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SDET / C</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b261687b5a0b3c2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SDET (Emerging Careers)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, S3, Data Lake, Kubernetes, CI/CD, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f14259ae5c6502a</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Oracle Data Platform Multi-Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Data Lake, Snowflake, Databricks, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec9153d45598c168</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AI Contact Center &amp; Virtual Agent Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Corpay</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74dbc3c4d17acbe3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Full Stack (Agentic AI)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=defa6c865beac825</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Software Engineer, Full Stack (Agentic AI)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3f2997ffc62fa69</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Full Stack (Agentic AI)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Marina del Rey, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8efbf8f2d86126a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Software Engineer, Full Stack (Agentic AI)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Marina del Rey, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fd48405ba3b6706</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, FAISS, Pinecone, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b1dd89d4530198e</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>S3, EC2, CI/CD, Terraform, Git, PostgreSQL, MySQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9a63c3b967e0200</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Data Engineer, Consultant</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Blue Shield of California</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Oakland, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, CI/CD, Snowflake, Databricks, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64dd02da75082641</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer (GenAI/ LLMs/ Agentic)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2b1a6f5a97d92f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior AI Security Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Information Technology Senior Management Forum</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Generative AI, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7f5f5ee2e79b80d</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Data Engineer - Vehicle Configuration Optimization</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Data Scientist, Data Lake, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b9156d1cac2aee9</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Sr. People Data Scientist</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SanDisk</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Milpitas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d71ed3ea56ec953</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Data Scientist - Conversational AI</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Git, BigQuery, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dcb602b7f6f09bdb</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-23.xlsx
+++ b/daily_matches/job_matches_2026-07-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Software Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Universal Background Screening</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, TensorFlow, PyTorch, MLflow, FastAPI, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>Copilot, S3, EC2, Glue, Redshift, Docker, CI/CD, Git, Redshift, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1589aadea1bbd4</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b2caf1308dae3d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Platform Engineer</t>
+          <t>GCP Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, MLflow, Docker, Kubernetes, CI/CD, Git</t>
+          <t>Data Scientist, Generative AI, RAG, BigQuery, Data Lake, Dataflow, BigQuery, Tableau, Power BI, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,207 +531,207 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd1f12311583f7b</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc84a59c47b9041</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Developer IV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Northramp</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe02b7c8ca17adb</t>
+          <t>https://www.indeed.com/viewjob?jk=d0cb3584a07ac501</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Software Engineer III - Java/Python/AWS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PyTorch, XGBoost, Docker, Kubernetes, Jenkins, Git, Kafka, NoSQL, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c7d8075142645e</t>
+          <t>https://www.indeed.com/viewjob?jk=dbd1082ecbb4b77c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Agentic AI</t>
+          <t>Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, FastAPI, Docker, CI/CD, Jenkins, GitHub Actions, Git, Kafka, Python</t>
+          <t>Data Scientist, RAG, Glue, Docker, CI/CD, Jenkins, Git, PySpark, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4462c6dfb49ebe52</t>
+          <t>https://www.indeed.com/viewjob?jk=a82cedf3a5c098bf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
+          <t>Software Engineer, Structured Storage</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, SQL, R, Java</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1feab28b0c3d3479</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffb8f2b64505893</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, SQL, R, Java</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c64848853e9c5d68</t>
+          <t>https://www.indeed.com/viewjob?jk=893e910c3bd5c112</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Git, PostgreSQL, MySQL, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Copilot, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=852061aed0a400e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a95a4ce3e78262</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c07301c3781026e</t>
+          <t>https://www.indeed.com/viewjob?jk=1b6b13a7348518f4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend (Agentic AI)</t>
+          <t>Systems Engineer I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Webster, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,147 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4794fc939dca2a43</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend (Agentic AI)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Marina del Rey, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b66613eeaa4e87b</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Backend (Agentic AI)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b80c70e76b63af34</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Backend (Agentic AI)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Marina del Rey, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00c5a256beb21635</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Software Engineer 3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>eBay</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, NoSQL, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=034831b9d1d4b137</t>
+          <t>https://www.indeed.com/viewjob?jk=887b1576ef6a1cff</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-23.xlsx
+++ b/daily_matches/job_matches_2026-07-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,130 +468,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer (Remote Opportunity)</t>
+          <t>Agentic AI Architect-Google Cloud</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Universal Background Screening</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Copilot, S3, EC2, Glue, Redshift, Docker, CI/CD, Git, Redshift, PostgreSQL</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Gemini, Prompt Engineering, BigQuery, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b2caf1308dae3d</t>
+          <t>https://www.indeed.com/viewjob?jk=9c971721d216ef56</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GCP Data Architect</t>
+          <t>Senior Software Engineer - Cloud Account Management</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, BigQuery, Data Lake, Dataflow, BigQuery, Tableau, Power BI, SQL</t>
+          <t>Data Scientist, RAG, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc84a59c47b9041</t>
+          <t>https://www.indeed.com/viewjob?jk=6116961d1246a18e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Developer IV</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>CALLISTOFUSION</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Prompt Engineering, Git, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0cb3584a07ac501</t>
+          <t>https://www.indeed.com/viewjob?jk=70464e2bce8f4e8d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - Java/Python/AWS</t>
+          <t>NCX Senior Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+          <t>TensorFlow, PyTorch, Kubernetes, CI/CD, Terraform, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbd1082ecbb4b77c</t>
+          <t>https://www.indeed.com/viewjob?jk=5328cb078658e928</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate</t>
+          <t>Senior Full Stack Software Engineer - Startpage</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>System1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Glue, Docker, CI/CD, Jenkins, Git, PySpark, Python, R</t>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,182 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82cedf3a5c098bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Software Engineer, Structured Storage</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Research Triangle Park, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, NoSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffb8f2b64505893</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Research Triangle Park, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, NoSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=893e910c3bd5c112</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Java Developer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Princeton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a95a4ce3e78262</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Rocket</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b6b13a7348518f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Systems Engineer I</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Paychex, Inc.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Webster, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=887b1576ef6a1cff</t>
+          <t>https://www.indeed.com/viewjob?jk=ec252f6dfba12db0</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-23.xlsx
+++ b/daily_matches/job_matches_2026-07-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Agentic AI Architect-Google Cloud</t>
+          <t>Gen. AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Gemini, Prompt Engineering, BigQuery, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Pinecone, Prompt Engineering, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c971721d216ef56</t>
+          <t>https://www.indeed.com/viewjob?jk=29fda9131139079e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Account Management</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6116961d1246a18e</t>
+          <t>https://www.indeed.com/viewjob?jk=5f87cbef2e8672c3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CALLISTOFUSION</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>21.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Prompt Engineering, Git, Python</t>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70464e2bce8f4e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0ffa581a9806f2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NCX Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>21.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Kubernetes, CI/CD, Terraform, Git, Python, R, Optimization</t>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,2282 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5328cb078658e928</t>
+          <t>https://www.indeed.com/viewjob?jk=a371c6a757e7cc60</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - Startpage</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>System1</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3c4dc88ae61fe0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f214eae45940a168</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ND, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2687a24e7dad6780</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ba2e28b0686e652</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4555ac252f371341</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c21907825eebf4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7237946dfe0583b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=801bb2fc81ed28a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ca8ef229b1532c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a6085a67377b69f</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7352e9be8f48d42</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DE, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=95dee7b8fef58b1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=630ac099235fbd6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SC, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1279bb37e0c78ee9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VT, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02f7accbf789b4d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2875a726636cc149</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44506379a420841e</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MS, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f29091cd781df40</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02feacdf4669a553</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f1b6022ed0acfd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AR, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efeae60730c199e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NE, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2460ff417a265bbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>KS, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d1f6380a3c4f83b</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NM, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9685333ed2d00ca8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21091337a312c8c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f893c944d1eaefab</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NV, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbf8f230bc8b0c83</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>WV, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cda9596586f3e32a</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20b5df003b7622a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8cd995cbc9be6f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CT, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6e4df8e6b664967</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AL, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa44bcb3004b69d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c0edbe0ca17f71c</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=833ff84fdbb1abd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbac48f07a9842df</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2eb1052d07321fc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c2fb4708a4607c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac0e9e73889131e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=176b93f1cf5124ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>WI, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9c8bd386e42843b</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>NH, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2e471cdb7ea8fe2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6ad11f79e7ed4e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MI, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a8935b313a478ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OK, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a7a4e1799edd25d</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>IA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7928d8310dc94518</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd1f237216b5ebbe</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Specialist - Architecture</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ea95a0e8ec56452</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer - Microservices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, BigQuery, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8dc6f74324ccd0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Specialist - Architecture</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LTM Limited</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, GCP Vertex AI, BigQuery, Data Lake, Dataflow, Git, BigQuery, PySpark, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=760cf46880d813e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Software Engineer - Corporate GenAI</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Generative AI, Prompt Engineering, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16819400a86897c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Data Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Bevi</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Charlestown, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Kinesis, AKS, CI/CD, Git, Snowflake, Kafka, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88024c4609faee60</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Data engineer with Java</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Intellibee Inc</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Malvern, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Glue, Redshift, Data Lake, Docker, Kubernetes, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b40731666819fe80</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Finance Data Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>IFS</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Copilot, CI/CD, Git, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=470c48d671a5aed8</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Senior Java Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Jenkins, Git, Kafka, R, Java</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6bf738c60c62b8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Java Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Jenkins, Git, Kafka, R, Java</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76a0805af660a7db</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Software Engineer-ELB</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>New Relic</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d438ac095207dfdb</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Decision Scientist - Specialty Operations</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Tableau, Power BI, Python, SQL, R, Optimization, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80362ae5ebba5e14</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Decision Scientist - Specialty Operations</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Tableau, Power BI, Python, SQL, R, Optimization, Hypothesis Testing, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7f474ed9457d47a</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>QA Automation Engineer - Robot Framework</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Concentrix</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec252f6dfba12db0</t>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf0a0f4e5478b748</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Software Engineer - Boomi Developer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, MySQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d7ed5f3c9898699</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Software Engineer - AI &amp; Cloud Engineering (Early to Mid Career</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Flexcompute Inc.</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Watertown, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff54522db739738a</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, ML Infrastructure- Online</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unity Technologies</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Olympia, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c52cbc513c7c8050</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>FanDuel</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Data Scientist, CI/CD, Databricks, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0124c68aa711e39</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>FanDuel</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Data Scientist, CI/CD, Databricks, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7403c7f190048d2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Machine Learning, Python</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Hudson, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7883302f74d8aa13</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-23.xlsx
+++ b/daily_matches/job_matches_2026-07-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. SW AI Engineer</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Pinecone, Prompt Engineering, Kubernetes, CI/CD</t>
+          <t>RAG, Redshift, Snowflake, Databricks, Redshift, Kafka, Hadoop, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf57225060415b23</t>
+          <t>https://www.indeed.com/viewjob?jk=4043ee460a725672</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Docker, CI/CD, Jenkins, Terraform, Git, MySQL</t>
+          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc1bf7c13d30efa0</t>
+          <t>https://www.indeed.com/viewjob?jk=12a7366a5fe55ec4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI ML Software Engineer - Data Platforms - Remote Nationwide or Hybrid in MN or DC</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Git, Snowflake, Databricks, Power BI, Python</t>
+          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afcebdc1e96b80ec</t>
+          <t>https://www.indeed.com/viewjob?jk=5543ba0ab775d610</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
+          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77b5f0b1a8f72889</t>
+          <t>https://www.indeed.com/viewjob?jk=a077af88e8069ec7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Application Engineer- Python/JavaScript/Typescript</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Egen Solutions Inc</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL</t>
+          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50cf2a5112831c1</t>
+          <t>https://www.indeed.com/viewjob?jk=76143d39ee35b355</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Science &amp; AI Solutions Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Cortex, AWS SageMaker, CI/CD, Git, Snowflake, Python, SQL</t>
+          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d018d3499b5a530f</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ed12d88cc2e877</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Jenkins, Git, Kafka, R, Java</t>
+          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5588d97b0802dcb7</t>
+          <t>https://www.indeed.com/viewjob?jk=eee1d8b4f35568a7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Java Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Kubernetes, CI/CD, Jenkins, Git, Kafka, R, Java</t>
+          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d3dc1e92354e313</t>
+          <t>https://www.indeed.com/viewjob?jk=be6ca4cb28d4f2ab</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Syracuse University</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dfd015014ed5a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=820aad6a65dfbe24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Surfaces Moments</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, BigQuery, BigQuery, Python, R, Optimization, A/B Testing</t>
+          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eecd3bd170d5e64f</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1bab104e859e83</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf2219ca946f5e65</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd44ba9ec2abfb8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Analytics &amp; Management - Officer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, AKS, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0da6cf211c70b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e5737811adca0295</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AI Engineer &amp; Full-Stack Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ACE Wellness Center</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
+          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d6cb71b4ff7e1b1</t>
+          <t>https://www.indeed.com/viewjob?jk=5dee030b01228d0d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dae8b24f2e228af</t>
+          <t>https://www.indeed.com/viewjob?jk=02eb3eef526fbc7e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Advanced Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Voicify</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Needham Heights, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, PyTorch, XGBoost, MLflow, CI/CD, Git, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=681c5b09ae8fb1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb5bccfe96e2cd1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Optimum Data Modeler - BSS Transformation</t>
+          <t>Senior AI Research Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, Snowflake, BigQuery, Kafka, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, PyTorch, YOLO, AWS SageMaker, Azure ML, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5993c3ad81ad4c85</t>
+          <t>https://www.indeed.com/viewjob?jk=483626571d6be4c0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer - Boomi Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Arm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, MySQL, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,42 +1056,497 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cadd5191edd52284</t>
+          <t>https://www.indeed.com/viewjob?jk=34b43cbdb247d166</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Machine Learning/Data Science</t>
+          <t>Senior Software Engineer, Data Acquisition</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>People Data Labs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bastrop, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ce03f58dc0c9d18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer III - PA085</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ZoomInfo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Waltham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Dataflow, Kubernetes, Apache Airflow, Terraform, Snowflake, BigQuery, Kafka, SQL</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c411d19dcc80f29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kronospan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Anniston, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e4dedeababce822</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI/ML Ops and Data Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Southlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, BigQuery, Dataflow, Docker, CI/CD, Git, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdb594873fc1ad66</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Machine Learning Ops Data Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Southlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, BigQuery, Dataflow, Docker, CI/CD, Git, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33e84a2e009cf57d</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Junior/Mid level Software Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Texas City, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LangChain, FastAPI, Docker, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29a0e4cdde39137f</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Scientist - Innovation - PhD</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Caris Life Sciences</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, PyTorch, S3, EC2, MLflow, Docker, Git, Python</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=772d02b82195dc39</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sr Specialist - Software Development &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, LLaMA, CI/CD, NoSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87cc317fb5aeaefc</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data and AI Engineer New</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Brown Gibbons Lang &amp; Company</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, CI/CD, Snowflake, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6506225563d57b7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Development Engineer - Workday Everywhere</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>10</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>PyTorch, OpenCV, PostgreSQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6427eea591329546</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=609d27118699b077</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sr. ServiceNow AI Agent Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, FastAPI, Docker, Kubernetes, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e765d07ff45bae24</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>WBG Pioneer - AI Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>World Bank Group</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d584bcdfdaf1cb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Corporate Treasury, New York, Associate, Software Engineering</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e54cb950546db26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mitti Cafe</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6727f7f8f2b7626</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-23.xlsx
+++ b/daily_matches/job_matches_2026-07-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>AWS Cloud AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Boston Medical Center</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Snowflake, Databricks, Redshift, Kafka, Hadoop, MySQL, MongoDB, Cassandra</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, S3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4043ee460a725672</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b96f6d08eb2e5b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+          <t>RAG, Redshift, Snowflake, Databricks, Redshift, Kafka, Hadoop, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12a7366a5fe55ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=c25594297d7dcd08</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer – AI &amp; Machine Learning</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Veryon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5543ba0ab775d610</t>
+          <t>https://www.indeed.com/viewjob?jk=426013248af00194</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+          <t>Data Scientist, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a077af88e8069ec7</t>
+          <t>https://www.indeed.com/viewjob?jk=462774f83d88a209</t>
         </is>
       </c>
     </row>
@@ -613,20 +613,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+          <t>Data Scientist, Generative AI, Synapse, Data Lake, MLflow, CI/CD, Git, Snowflake, Databricks, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76143d39ee35b355</t>
+          <t>https://www.indeed.com/viewjob?jk=d071a80499173a38</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Analytics Platform</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ed12d88cc2e877</t>
+          <t>https://www.indeed.com/viewjob?jk=52bd230153d8b27f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI / ML Solutions Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Fort Walton Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Glue, Docker, CI/CD, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee1d8b4f35568a7</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2e3eeb305c2114</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cybersecurity &amp; AI/Data Governance Intern</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Boston Medical Center</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6ca4cb28d4f2ab</t>
+          <t>https://www.indeed.com/viewjob?jk=cafa27182206ba1e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=820aad6a65dfbe24</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e8b25e2f2a2f9a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Forward Deployed Engineer (FDE) - AI Native Analyst - Dallas ATC - NAELFY26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, CI/CD, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1bab104e859e83</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c817e404b8fe0e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior QA Engineer - Airvoyant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>TRAX USA Corp.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Coral Gables, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+          <t>Generative AI, S3, EC2, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd44ba9ec2abfb8</t>
+          <t>https://www.indeed.com/viewjob?jk=38ee81c497706d67</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Scientist, Ops Research</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+          <t>Data Scientist, RAG, Azure ML, Git, Snowflake, Databricks, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5737811adca0295</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfd9f37dd69062a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Bold Reuse</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+          <t>Copilot, S3, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dee030b01228d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=b7de5e741a0a6d4e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Forward Deployed AI Engineer (GenAI, AWS)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Kafka, Python</t>
+          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02eb3eef526fbc7e</t>
+          <t>https://www.indeed.com/viewjob?jk=51b5906561b2799c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Advanced Data Scientist</t>
+          <t>Senior Forward Deployed AI Engineer (GenAI, AWS)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, PyTorch, XGBoost, MLflow, CI/CD, Git, Databricks, PySpark, Python</t>
+          <t>AI Engineer, PyTorch, Data Lake, MLflow, Kubernetes, CI/CD, Terraform, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fb5bccfe96e2cd1</t>
+          <t>https://www.indeed.com/viewjob?jk=19b7e52c5f7a80bd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI Research Engineer</t>
+          <t>Gen AI Developer Specialist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, PyTorch, YOLO, AWS SageMaker, Azure ML, MLflow, Docker, Kubernetes</t>
+          <t>RAG, Prompt Engineering, S3, Git, Kafka, NoSQL, Python, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483626571d6be4c0</t>
+          <t>https://www.indeed.com/viewjob?jk=48771f9356feeed9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Scientist I, Consumer Data Intelligence, L'Oréal Research &amp; Innovation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Arm</t>
+          <t>L'Oréal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Clark, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b43cbdb247d166</t>
+          <t>https://www.indeed.com/viewjob?jk=978f3a075403d93d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Acquisition</t>
+          <t>Senior Marketing Automation Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>People Data Labs</t>
+          <t>Twin Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, Python, SQL</t>
+          <t>RAG, S3, Git, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce03f58dc0c9d18</t>
+          <t>https://www.indeed.com/viewjob?jk=a69e308750f29daf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer III - PA085</t>
+          <t>Senior MLOps Engineer- Remote[Candidates must work PST hours]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, Kubernetes, Apache Airflow, Terraform, Snowflake, BigQuery, Kafka, SQL</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c411d19dcc80f29</t>
+          <t>https://www.indeed.com/viewjob?jk=94542bafff84287f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>AI/ML Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kronospan</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Anniston, AL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Power BI, Python, SQL, R</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, Kubernetes, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4dedeababce822</t>
+          <t>https://www.indeed.com/viewjob?jk=3244267518077a47</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI/ML Ops and Data Engineer</t>
+          <t>Technology Engineer Sr (Java/Angular/REACT)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, BigQuery, Dataflow, Docker, CI/CD, Git, BigQuery, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, Git, MongoDB, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb594873fc1ad66</t>
+          <t>https://www.indeed.com/viewjob?jk=e76f06aa8d709b45</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Machine Learning Ops Data Engineer</t>
+          <t>Analyst, Applied AI Solutions</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, BigQuery, Dataflow, Docker, CI/CD, Git, BigQuery, Python, SQL, R</t>
+          <t>RAG, Gemini, Copilot, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e84a2e009cf57d</t>
+          <t>https://www.indeed.com/viewjob?jk=f59ed3133ac7bf35</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Junior/Mid level Software Engineer</t>
+          <t>Data Scientist - Strategic Network Design</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Best Buy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LangChain, FastAPI, Docker, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, PySpark, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29a0e4cdde39137f</t>
+          <t>https://www.indeed.com/viewjob?jk=37329089afb29783</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Scientist - Innovation - PhD</t>
+          <t>Data Scientist - AI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Infoblox</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tacoma, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, PyTorch, S3, EC2, MLflow, Docker, Git, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,252 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772d02b82195dc39</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Sr Specialist - Software Development &amp; Engineering</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Charles Schwab</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, LLaMA, CI/CD, NoSQL, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87cc317fb5aeaefc</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Data and AI Engineer New</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Brown Gibbons Lang &amp; Company</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AI Engineer, Copilot, CI/CD, Snowflake, Tableau, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6506225563d57b7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Software Development Engineer - Workday Everywhere</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Workday</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Boulder, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=609d27118699b077</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Sr. ServiceNow AI Agent Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, LLaMA, FastAPI, Docker, Kubernetes, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e765d07ff45bae24</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>WBG Pioneer - AI Engineer Intern</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>World Bank Group</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0d584bcdfdaf1cb0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Corporate Treasury, New York, Associate, Software Engineering</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e54cb950546db26</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Mitti Cafe</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6727f7f8f2b7626</t>
+          <t>https://www.indeed.com/viewjob?jk=33b3e3b99043e283</t>
         </is>
       </c>
     </row>
